--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487774_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487774_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5665</v>
+        <v>3.161</v>
       </c>
       <c r="E2" t="n">
-        <v>2.925</v>
+        <v>3.4608</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3585</v>
+        <v>-0.2998</v>
       </c>
       <c r="G2" t="n">
         <v>1.4867</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2096</v>
+        <v>-0.6151</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.901</v>
+        <v>-0.3652</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3085</v>
+        <v>-0.2498</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5417</v>
+        <v>2.2995</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5509</v>
+        <v>2.0151</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0092</v>
+        <v>0.2844</v>
       </c>
       <c r="G3" t="n">
         <v>0.6219</v>
@@ -688,13 +688,13 @@
         <v>2.4974</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3543</v>
+        <v>-0.5965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4096</v>
+        <v>-0.1261</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7639</v>
+        <v>-0.4703</v>
       </c>
       <c r="V3" t="n">
         <v>0.8173</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6478</v>
+        <v>0.4501</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1428</v>
+        <v>1.9628</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.495</v>
+        <v>-1.5127</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0997</v>
+        <v>-1.019</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8295</v>
+        <v>-0.5863</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2702</v>
+        <v>-0.4327</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8763</v>
+        <v>1.9817</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7587</v>
+        <v>1.2428</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1176</v>
+        <v>0.7388</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.976</v>
+        <v>-3.0007</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5882</v>
+        <v>-1.8291</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3878</v>
+        <v>-1.1716</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3719</v>
+        <v>-0.2649</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1396</v>
+        <v>-0.2519</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2323</v>
+        <v>-0.013</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1675</v>
+        <v>0.6934</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>1.2737</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5802</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4208</v>
+        <v>0.2177</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9628</v>
+        <v>1.0356</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5421</v>
+        <v>-0.8179</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.019</v>
+        <v>-1.0997</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5863</v>
+        <v>-0.8295</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4327</v>
+        <v>-0.2702</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9817</v>
+        <v>0.8763</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2428</v>
+        <v>0.7587</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7388</v>
+        <v>0.1176</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0007</v>
+        <v>-1.976</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8291</v>
+        <v>-1.5882</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1716</v>
+        <v>-0.3878</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2943</v>
+        <v>-0.0582</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2519</v>
+        <v>0.0324</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0424</v>
+        <v>-0.0906</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6934</v>
+        <v>1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2737</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8452</v>
+        <v>-1.4841</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.537</v>
+        <v>-2.3226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6918</v>
+        <v>0.8386</v>
       </c>
       <c r="G6" t="n">
         <v>-1.801</v>
@@ -922,13 +922,13 @@
         <v>2.7055</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7751</v>
+        <v>-0.414</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6277</v>
+        <v>-0.4133</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9340000000000001</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9921</v>
+        <v>-2.162</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7206</v>
+        <v>0.0384</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2715</v>
+        <v>-2.2004</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2292</v>
+        <v>-1.0434</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3204</v>
+        <v>-0.0106</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9088</v>
+        <v>-1.0328</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3346</v>
+        <v>0.0384</v>
       </c>
       <c r="K7" t="n">
-        <v>0.223</v>
+        <v>0.0384</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5576</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8945</v>
+        <v>-1.0818</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5434</v>
+        <v>-0.049</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3512</v>
+        <v>-1.0328</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2893</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3386</v>
+        <v>0.0489</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5129</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8515</v>
+        <v>0.0489</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3503</v>
+        <v>-1.1675</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5178</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1914</v>
+        <v>-2.5627</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0384</v>
+        <v>0.0173</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2297</v>
+        <v>-2.5801</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0434</v>
+        <v>-1.6815</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0106</v>
+        <v>-1.2643</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0328</v>
+        <v>-0.4172</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0384</v>
+        <v>1.1884</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0384</v>
+        <v>0.6096</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.5788</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0818</v>
+        <v>-2.87</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.049</v>
+        <v>-1.874</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0328</v>
+        <v>-0.996</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0196</v>
+        <v>-0.5934</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.3605</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0196</v>
+        <v>-0.2329</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1675</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-0.9340000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
+        <v>-2.7936</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.9349</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.8587</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.2292</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.3204</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.9088</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.3346</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.5576</v>
+      </c>
+      <c r="M9" t="n">
         <v>-2.8945</v>
       </c>
-      <c r="E9" t="n">
-        <v>-0.197</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-2.6975</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.6815</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1.2643</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.4172</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.1884</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.6096</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5788</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-2.87</v>
-      </c>
       <c r="N9" t="n">
-        <v>-1.874</v>
+        <v>-1.5434</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.996</v>
+        <v>-1.3512</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9251</v>
+        <v>-0.4629</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5748</v>
+        <v>-0.7272</v>
       </c>
       <c r="U9" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="V9" t="n">
         <v>-0.3503</v>
       </c>
-      <c r="V9" t="n">
-        <v>-0.7040999999999999</v>
-      </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9235</v>
+        <v>-3.7423</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.661</v>
+        <v>-2.3499</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2625</v>
+        <v>-1.3924</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7762</v>
+        <v>-2.8375</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2176</v>
+        <v>-0.8806</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9937</v>
+        <v>-1.957</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4493</v>
+        <v>-1.025</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9402</v>
+        <v>-0.3498</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3896</v>
+        <v>-0.6752</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3268</v>
+        <v>-1.8126</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7227</v>
+        <v>-0.5308</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6041</v>
+        <v>-1.2818</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6649</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2525</v>
+        <v>-0.2804</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1305</v>
+        <v>-0.2843</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.122</v>
+        <v>0.0039</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9375</v>
+        <v>-3.8457</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.457</v>
+        <v>-2.5538</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4805</v>
+        <v>-1.2919</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8375</v>
+        <v>-1.7762</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8806</v>
+        <v>0.2176</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.957</v>
+        <v>-1.9937</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.025</v>
+        <v>-0.4493</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3498</v>
+        <v>0.9402</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6752</v>
+        <v>-1.3896</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8126</v>
+        <v>-1.3268</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5308</v>
+        <v>-0.7227</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2818</v>
+        <v>-0.6041</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6244</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R11" t="n">
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4756</v>
+        <v>-0.1747</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3915</v>
+        <v>-0.0233</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0842</v>
+        <v>-0.1513</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3322</v>
+        <v>-4.4775</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3501</v>
+        <v>-3.6716</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9821</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.052</v>
@@ -1390,13 +1390,13 @@
         <v>2.2893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.094</v>
+        <v>-0.2393</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4625</v>
+        <v>0.141</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5565</v>
+        <v>-0.3803</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3538</v>
@@ -1426,7 +1426,7 @@
         <v>-14.9396</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.302800000000001</v>
+        <v>-3.3028</v>
       </c>
       <c r="F13" t="n">
         <v>-11.6368</v>
@@ -1438,10 +1438,10 @@
         <v>-10.267</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.163900000000001</v>
+        <v>-5.163899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.513000000000002</v>
+        <v>5.513000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>3.226900000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-13.4941</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.449699999999999</v>
+        <v>-7.4497</v>
       </c>
       <c r="P13" t="n">
         <v>5.2028</v>
@@ -1468,13 +1468,13 @@
         <v>17.6899</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6504</v>
+        <v>-3.650500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3786</v>
+        <v>-2.3784</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2718</v>
+        <v>-1.2717</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0615</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.0836</v>
+        <v>10.4965</v>
       </c>
       <c r="E14" t="n">
         <v>8.645200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4384</v>
+        <v>1.8512</v>
       </c>
       <c r="G14" t="n">
         <v>4.7541</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3701</v>
+        <v>0.7829</v>
       </c>
       <c r="T14" t="n">
         <v>0.1924</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1777</v>
+        <v>0.5905</v>
       </c>
       <c r="V14" t="n">
         <v>3.5026</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.5982</v>
+        <v>7.2012</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7967</v>
+        <v>4.4037</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8015</v>
+        <v>2.7976</v>
       </c>
       <c r="G15" t="n">
         <v>5.4191</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8034</v>
+        <v>1.4064</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9441</v>
+        <v>0.5511</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8593</v>
+        <v>0.8554</v>
       </c>
       <c r="V15" t="n">
         <v>0.5838</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6346</v>
+        <v>5.0187</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2306</v>
+        <v>5.1234</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.596</v>
+        <v>-0.1047</v>
       </c>
       <c r="G16" t="n">
         <v>3.2865</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0463</v>
+        <v>0.3378</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1083</v>
+        <v>0.383</v>
       </c>
       <c r="V16" t="n">
         <v>0.3538</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4213</v>
+        <v>2.2483</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7352</v>
+        <v>1.9495</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3139</v>
+        <v>0.2987</v>
       </c>
       <c r="G17" t="n">
         <v>4.9006</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4169</v>
+        <v>0.41</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.199</v>
+        <v>0.0153</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2179</v>
+        <v>0.3948</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3975</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5949</v>
+        <v>0.9403</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4019</v>
+        <v>-0.759</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9968</v>
+        <v>1.6993</v>
       </c>
       <c r="G18" t="n">
         <v>1.5027</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4678</v>
+        <v>0.8133</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8482</v>
+        <v>-0.2052</v>
       </c>
       <c r="U18" t="n">
-        <v>1.316</v>
+        <v>1.0185</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2533</v>
+        <v>0.8439</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9169</v>
+        <v>1.4527</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6636</v>
+        <v>-0.6088</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1941</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3445</v>
+        <v>0.2461</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3262</v>
+        <v>0.2096</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0183</v>
+        <v>0.0365</v>
       </c>
       <c r="V19" t="n">
         <v>1.1675</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1412</v>
+        <v>0.3271</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7769</v>
+        <v>-2.4554</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6357</v>
+        <v>2.7825</v>
       </c>
       <c r="G20" t="n">
         <v>1.6002</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0078</v>
+        <v>0.4761</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4567</v>
+        <v>-0.1352</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4645</v>
+        <v>0.6113</v>
       </c>
       <c r="V20" t="n">
         <v>0.1238</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.345</v>
+        <v>-1.3577</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5511</v>
+        <v>-0.7654</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.5923</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4061</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2068</v>
+        <v>0.1941</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4534</v>
+        <v>0.2391</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2466</v>
+        <v>-0.045</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0787</v>
+        <v>-3.1208</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0892</v>
+        <v>-3.3035</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0106</v>
+        <v>0.1828</v>
       </c>
       <c r="G22" t="n">
         <v>1.7537</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3706</v>
+        <v>0.3285</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4534</v>
+        <v>0.2391</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0828</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0815</v>
+        <v>-6.2291</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8688</v>
+        <v>-2.6545</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2127</v>
+        <v>-3.5746</v>
       </c>
       <c r="G23" t="n">
         <v>-4.186</v>
@@ -2248,13 +2248,13 @@
         <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7685</v>
+        <v>0.0838</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0033</v>
+        <v>0.211</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7652</v>
+        <v>-0.1272</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3351</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.9395</v>
+        <v>16.3684</v>
       </c>
       <c r="E24" t="n">
         <v>11.6367</v>
       </c>
       <c r="F24" t="n">
-        <v>3.3029</v>
+        <v>4.7317</v>
       </c>
       <c r="G24" t="n">
         <v>15.4307</v>
@@ -2326,13 +2326,13 @@
         <v>12.4872</v>
       </c>
       <c r="S24" t="n">
-        <v>3.650299999999999</v>
+        <v>5.079000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2718</v>
+        <v>1.272</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3784</v>
+        <v>3.807199999999999</v>
       </c>
       <c r="V24" t="n">
         <v>1.0614</v>
